--- a/oe2027-conferencia.xlsx
+++ b/oe2027-conferencia.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="616">
   <si>
     <t xml:space="preserve">OE 2027 — valores para conferência</t>
   </si>
@@ -337,16 +337,55 @@
     <t xml:space="preserve">Fonte: Relatório OE2027, Quadro 4.4, pág. 72 do PDF (pág. impressa 56)</t>
   </si>
   <si>
-    <t xml:space="preserve">IVA (Imposto sobre o Valor Acrescentado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRS (Rendimento das pessoas singulares)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRC (Rendimento das pessoas coletivas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISP (Produtos petrolíferos e energéticos)</t>
+    <t xml:space="preserve">IVA (Imposto sobre o Valor Acrescentado, pago no consumo de bens e serviços)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRS (Imposto sobre o rendimento das pessoas: salários, pensões, rendas, mais-valias)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRC (Imposto sobre o lucro das empresas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISP (Imposto sobre os produtos petrolíferos e energéticos, pago sobretudo nos combustíveis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imposto do Selo (Incide sobre contratos, crédito, seguros e outras operações)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imposto sobre o tabaco (Imposto especial sobre cigarros e outros produtos de tabaco)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IUC (Imposto único de circulação, pago todos os anos por quem tem um veículo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impostos sobre veículos (ISV, pago quando um veículo é matriculado em Portugal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outros impostos diretos (Contribuições setoriais, como energia e banca, e adicional ao IMI (CESE, AIMI, CSB, CST))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IABA (Imposto sobre o álcool, as bebidas alcoólicas e as bebidas açucaradas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outros impostos indiretos (Contribuições da indústria farmacêutica, dos dispositivos médicos e do audiovisual (CEIF, CEFID, CAV))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Despesa fiscal do Estado por imposto (benefícios fiscais)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonte: Relatório OE2027, Quadro 4.5, pág. 76 do PDF (pág. impressa 60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISP</t>
   </si>
   <si>
     <t xml:space="preserve">Imposto do Selo</t>
@@ -355,39 +394,6 @@
     <t xml:space="preserve">Imposto sobre o tabaco</t>
   </si>
   <si>
-    <t xml:space="preserve">IUC (Imposto único de circulação)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impostos sobre veículos (ISV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outros impostos diretos (CESE, AIMI, CSB, CST)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IABA (Álcool e bebidas açucaradas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outros impostos indiretos (CEIF, CEFID, CAV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Despesa fiscal do Estado por imposto (benefícios fiscais)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonte: Relatório OE2027, Quadro 4.5, pág. 76 do PDF (pág. impressa 60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISP</t>
-  </si>
-  <si>
     <t xml:space="preserve">IUC</t>
   </si>
   <si>
@@ -812,6 +818,9 @@
   </si>
   <si>
     <t xml:space="preserve">Saldo global na fonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A linha «Pensões» é transcrita tal como no quadro. Sobrevivência (3 598,2) e invalidez (1 476,0) têm linhas próprias e as linhas do Quadro 4.17 não reconciliam com o total das despesas correntes, pelo que não é possível confirmar se já estão incluídas.</t>
   </si>
   <si>
     <t xml:space="preserve">Principais medidas de política orçamental com impacto em 2027 (M€)</t>
@@ -2529,50 +2538,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>63</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2614,7 +2623,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>2440355752</v>
@@ -2673,10 +2682,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C8" s="22" t="n">
         <v>11260338</v>
@@ -2713,10 +2722,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C9" s="22" t="n">
         <v>6969447</v>
@@ -2753,10 +2762,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>10109570</v>
@@ -2793,10 +2802,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>307</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>304</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>10996877</v>
@@ -2833,10 +2842,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>4192547</v>
@@ -2873,10 +2882,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>8821665</v>
@@ -2913,10 +2922,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C14" s="22" t="n">
         <v>5132622</v>
@@ -2953,10 +2962,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C15" s="22" t="n">
         <v>9439509</v>
@@ -2993,10 +3002,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C16" s="22" t="n">
         <v>3035644</v>
@@ -3033,10 +3042,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C17" s="22" t="n">
         <v>6972427</v>
@@ -3073,10 +3082,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C18" s="22" t="n">
         <v>3612905</v>
@@ -3113,10 +3122,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C19" s="22" t="n">
         <v>16416889</v>
@@ -3153,10 +3162,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C20" s="22" t="n">
         <v>7745937</v>
@@ -3193,10 +3202,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C21" s="22" t="n">
         <v>5304980</v>
@@ -3233,10 +3242,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C22" s="22" t="n">
         <v>20153508</v>
@@ -3273,10 +3282,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C23" s="22" t="n">
         <v>3273622</v>
@@ -3313,10 +3322,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C24" s="22" t="n">
         <v>6360101</v>
@@ -3353,10 +3362,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C25" s="22" t="n">
         <v>5792729</v>
@@ -3393,10 +3402,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>8203678</v>
@@ -3433,10 +3442,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C27" s="22" t="n">
         <v>7606956</v>
@@ -3473,10 +3482,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C28" s="22" t="n">
         <v>10722094</v>
@@ -3513,10 +3522,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C29" s="22" t="n">
         <v>3456131</v>
@@ -3553,10 +3562,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>326</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>323</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>3364651</v>
@@ -3593,10 +3602,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C31" s="22" t="n">
         <v>14533112</v>
@@ -3633,10 +3642,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C32" s="22" t="n">
         <v>8814415</v>
@@ -3673,10 +3682,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C33" s="22" t="n">
         <v>4067939</v>
@@ -3713,10 +3722,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C34" s="22" t="n">
         <v>7852021</v>
@@ -3753,10 +3762,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C35" s="22" t="n">
         <v>14171299</v>
@@ -3793,10 +3802,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C36" s="22" t="n">
         <v>14172141</v>
@@ -3833,10 +3842,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C37" s="22" t="n">
         <v>21090044</v>
@@ -3873,10 +3882,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C38" s="22" t="n">
         <v>7936357</v>
@@ -3913,10 +3922,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C39" s="22" t="n">
         <v>14632002</v>
@@ -3953,10 +3962,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C40" s="22" t="n">
         <v>5264712</v>
@@ -3993,10 +4002,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C41" s="22" t="n">
         <v>7945050</v>
@@ -4033,10 +4042,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C42" s="22" t="n">
         <v>33691650</v>
@@ -4073,10 +4082,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C43" s="22" t="n">
         <v>13006004</v>
@@ -4113,10 +4122,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C44" s="22" t="n">
         <v>10322268</v>
@@ -4153,10 +4162,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="C45" s="22" t="n">
         <v>11803843</v>
@@ -4193,10 +4202,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C46" s="22" t="n">
         <v>3736198</v>
@@ -4233,10 +4242,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C47" s="22" t="n">
         <v>18170141</v>
@@ -4273,10 +4282,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C48" s="22" t="n">
         <v>24444736</v>
@@ -4313,10 +4322,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C49" s="22" t="n">
         <v>9563828</v>
@@ -4353,10 +4362,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C50" s="22" t="n">
         <v>7559022</v>
@@ -4393,10 +4402,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C51" s="22" t="n">
         <v>8419670</v>
@@ -4433,10 +4442,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C52" s="22" t="n">
         <v>20379865</v>
@@ -4473,10 +4482,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C53" s="22" t="n">
         <v>18447169</v>
@@ -4513,10 +4522,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C54" s="22" t="n">
         <v>6530556</v>
@@ -4553,10 +4562,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C55" s="22" t="n">
         <v>5760978</v>
@@ -4593,10 +4602,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C56" s="22" t="n">
         <v>17523218</v>
@@ -4633,10 +4642,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C57" s="22" t="n">
         <v>6902802</v>
@@ -4673,10 +4682,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C58" s="22" t="n">
         <v>6074782</v>
@@ -4713,10 +4722,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>351</v>
       </c>
       <c r="C59" s="22" t="n">
         <v>12129117</v>
@@ -4753,10 +4762,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C60" s="22" t="n">
         <v>7805281</v>
@@ -4793,10 +4802,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C61" s="22" t="n">
         <v>12149578</v>
@@ -4833,10 +4842,10 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C62" s="22" t="n">
         <v>10296237</v>
@@ -4873,10 +4882,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C63" s="22" t="n">
         <v>7564582</v>
@@ -4913,10 +4922,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C64" s="22" t="n">
         <v>6068426</v>
@@ -4953,10 +4962,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C65" s="22" t="n">
         <v>7382694</v>
@@ -4993,10 +5002,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C66" s="22" t="n">
         <v>11498188</v>
@@ -5033,10 +5042,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C67" s="22" t="n">
         <v>5109883</v>
@@ -5073,10 +5082,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C68" s="22" t="n">
         <v>19074690</v>
@@ -5113,10 +5122,10 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C69" s="22" t="n">
         <v>17580105</v>
@@ -5153,10 +5162,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C70" s="22" t="n">
         <v>15165978</v>
@@ -5193,10 +5202,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B71" s="6" t="s">
         <v>366</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>363</v>
       </c>
       <c r="C71" s="22" t="n">
         <v>14731422</v>
@@ -5233,10 +5242,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C72" s="22" t="n">
         <v>7354186</v>
@@ -5273,10 +5282,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C73" s="22" t="n">
         <v>8430788</v>
@@ -5313,10 +5322,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C74" s="22" t="n">
         <v>7691324</v>
@@ -5353,10 +5362,10 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C75" s="22" t="n">
         <v>10555325</v>
@@ -5393,10 +5402,10 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C76" s="22" t="n">
         <v>3917933</v>
@@ -5433,10 +5442,10 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C77" s="22" t="n">
         <v>4893342</v>
@@ -5473,10 +5482,10 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C78" s="22" t="n">
         <v>7565431</v>
@@ -5513,10 +5522,10 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C79" s="22" t="n">
         <v>8634383</v>
@@ -5553,10 +5562,10 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C80" s="22" t="n">
         <v>7285860</v>
@@ -5593,10 +5602,10 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C81" s="22" t="n">
         <v>5419923</v>
@@ -5633,10 +5642,10 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>377</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>374</v>
       </c>
       <c r="C82" s="22" t="n">
         <v>6379973</v>
@@ -5673,10 +5682,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C83" s="22" t="n">
         <v>4727663</v>
@@ -5713,10 +5722,10 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C84" s="22" t="n">
         <v>6261700</v>
@@ -5753,10 +5762,10 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C85" s="22" t="n">
         <v>4580690</v>
@@ -5793,10 +5802,10 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C86" s="22" t="n">
         <v>6488410</v>
@@ -5833,10 +5842,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C87" s="22" t="n">
         <v>11076604</v>
@@ -5873,10 +5882,10 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C88" s="22" t="n">
         <v>9363304</v>
@@ -5913,10 +5922,10 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C89" s="22" t="n">
         <v>6315665</v>
@@ -5953,10 +5962,10 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C90" s="22" t="n">
         <v>6827303</v>
@@ -5993,10 +6002,10 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C91" s="22" t="n">
         <v>4583606</v>
@@ -6033,10 +6042,10 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C92" s="22" t="n">
         <v>9891894</v>
@@ -6073,10 +6082,10 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C93" s="22" t="n">
         <v>7011388</v>
@@ -6113,10 +6122,10 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C94" s="22" t="n">
         <v>4422334</v>
@@ -6153,10 +6162,10 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C95" s="22" t="n">
         <v>7235778</v>
@@ -6193,10 +6202,10 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C96" s="22" t="n">
         <v>7627181</v>
@@ -6233,10 +6242,10 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C97" s="22" t="n">
         <v>4983404</v>
@@ -6273,10 +6282,10 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>394</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>391</v>
       </c>
       <c r="C98" s="22" t="n">
         <v>9529656</v>
@@ -6313,10 +6322,10 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C99" s="22" t="n">
         <v>13135534</v>
@@ -6353,10 +6362,10 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C100" s="22" t="n">
         <v>13511320</v>
@@ -6393,10 +6402,10 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C101" s="22" t="n">
         <v>5271043</v>
@@ -6433,10 +6442,10 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C102" s="22" t="n">
         <v>3733256</v>
@@ -6473,10 +6482,10 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C103" s="22" t="n">
         <v>7725731</v>
@@ -6513,10 +6522,10 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C104" s="22" t="n">
         <v>6101030</v>
@@ -6553,10 +6562,10 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C105" s="22" t="n">
         <v>6297128</v>
@@ -6593,10 +6602,10 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C106" s="22" t="n">
         <v>5249534</v>
@@ -6633,10 +6642,10 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C107" s="22" t="n">
         <v>5443874</v>
@@ -6673,10 +6682,10 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C108" s="22" t="n">
         <v>5170168</v>
@@ -6713,10 +6722,10 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C109" s="22" t="n">
         <v>274135</v>
@@ -6753,10 +6762,10 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C110" s="22" t="n">
         <v>6645989</v>
@@ -6793,10 +6802,10 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C111" s="22" t="n">
         <v>4904357</v>
@@ -6833,10 +6842,10 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B112" s="6" t="s">
         <v>408</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>405</v>
       </c>
       <c r="C112" s="22" t="n">
         <v>3436547</v>
@@ -6873,10 +6882,10 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C113" s="22" t="n">
         <v>2523642</v>
@@ -6913,10 +6922,10 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C114" s="22" t="n">
         <v>426502</v>
@@ -6953,10 +6962,10 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C115" s="22" t="n">
         <v>0</v>
@@ -6993,10 +7002,10 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C116" s="22" t="n">
         <v>0</v>
@@ -7033,10 +7042,10 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="6" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C117" s="22" t="n">
         <v>8010782</v>
@@ -7073,10 +7082,10 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C118" s="22" t="n">
         <v>5982151</v>
@@ -7113,10 +7122,10 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C119" s="22" t="n">
         <v>0</v>
@@ -7153,10 +7162,10 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C120" s="22" t="n">
         <v>3187585</v>
@@ -7193,10 +7202,10 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C121" s="22" t="n">
         <v>8347171</v>
@@ -7233,10 +7242,10 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C122" s="22" t="n">
         <v>5828195</v>
@@ -7273,10 +7282,10 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C123" s="22" t="n">
         <v>3024068</v>
@@ -7313,10 +7322,10 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C124" s="22" t="n">
         <v>1586027</v>
@@ -7353,10 +7362,10 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C125" s="22" t="n">
         <v>5945968</v>
@@ -7393,10 +7402,10 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C126" s="22" t="n">
         <v>7710436</v>
@@ -7433,10 +7442,10 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C127" s="22" t="n">
         <v>6908051</v>
@@ -7473,10 +7482,10 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B128" s="6" t="s">
         <v>424</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>421</v>
       </c>
       <c r="C128" s="22" t="n">
         <v>7658614</v>
@@ -7513,10 +7522,10 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C129" s="22" t="n">
         <v>4436408</v>
@@ -7553,10 +7562,10 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="6" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C130" s="22" t="n">
         <v>8761229</v>
@@ -7593,10 +7602,10 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C131" s="22" t="n">
         <v>14932395</v>
@@ -7633,10 +7642,10 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C132" s="22" t="n">
         <v>3877679</v>
@@ -7673,10 +7682,10 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="6" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C133" s="22" t="n">
         <v>5530414</v>
@@ -7713,10 +7722,10 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="6" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C134" s="22" t="n">
         <v>9023405</v>
@@ -7753,10 +7762,10 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="6" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C135" s="22" t="n">
         <v>13920241</v>
@@ -7793,10 +7802,10 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C136" s="22" t="n">
         <v>12634265</v>
@@ -7833,10 +7842,10 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C137" s="22" t="n">
         <v>8592170</v>
@@ -7873,10 +7882,10 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C138" s="22" t="n">
         <v>6473830</v>
@@ -7913,10 +7922,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C139" s="22" t="n">
         <v>7917404</v>
@@ -7953,10 +7962,10 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="6" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C140" s="22" t="n">
         <v>5912074</v>
@@ -7993,10 +8002,10 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C141" s="22" t="n">
         <v>7151789</v>
@@ -8033,10 +8042,10 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B142" s="6" t="s">
         <v>438</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>435</v>
       </c>
       <c r="C142" s="22" t="n">
         <v>4101404</v>
@@ -8073,10 +8082,10 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="6" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C143" s="22" t="n">
         <v>3690788</v>
@@ -8113,10 +8122,10 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="6" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C144" s="22" t="n">
         <v>5359397</v>
@@ -8153,10 +8162,10 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="6" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C145" s="22" t="n">
         <v>3130222</v>
@@ -8193,10 +8202,10 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="6" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C146" s="22" t="n">
         <v>4645406</v>
@@ -8233,10 +8242,10 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C147" s="22" t="n">
         <v>10794787</v>
@@ -8273,10 +8282,10 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C148" s="22" t="n">
         <v>6044350</v>
@@ -8313,10 +8322,10 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="6" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C149" s="22" t="n">
         <v>2727073</v>
@@ -8353,10 +8362,10 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C150" s="22" t="n">
         <v>2027253</v>
@@ -8393,10 +8402,10 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="6" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C151" s="22" t="n">
         <v>3874989</v>
@@ -8433,10 +8442,10 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="6" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C152" s="22" t="n">
         <v>4026619</v>
@@ -8473,10 +8482,10 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="6" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C153" s="22" t="n">
         <v>13273694</v>
@@ -8513,10 +8522,10 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="6" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C154" s="22" t="n">
         <v>9020741</v>
@@ -8553,10 +8562,10 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="6" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C155" s="22" t="n">
         <v>6647639</v>
@@ -8593,10 +8602,10 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="6" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C156" s="22" t="n">
         <v>16018151</v>
@@ -8633,10 +8642,10 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="6" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C157" s="22" t="n">
         <v>3453668</v>
@@ -8673,10 +8682,10 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="B158" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>451</v>
       </c>
       <c r="C158" s="22" t="n">
         <v>4780336</v>
@@ -8713,10 +8722,10 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="6" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C159" s="22" t="n">
         <v>5934988</v>
@@ -8753,10 +8762,10 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="6" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C160" s="22" t="n">
         <v>0</v>
@@ -8793,10 +8802,10 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C161" s="22" t="n">
         <v>0</v>
@@ -8833,10 +8842,10 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="6" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C162" s="22" t="n">
         <v>11461363</v>
@@ -8873,10 +8882,10 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="6" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C163" s="22" t="n">
         <v>4838105</v>
@@ -8913,10 +8922,10 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="6" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C164" s="22" t="n">
         <v>82594</v>
@@ -8953,10 +8962,10 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="6" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C165" s="22" t="n">
         <v>8419545</v>
@@ -8993,10 +9002,10 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="6" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C166" s="22" t="n">
         <v>0</v>
@@ -9033,10 +9042,10 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="6" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C167" s="22" t="n">
         <v>19558451</v>
@@ -9073,10 +9082,10 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="6" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C168" s="22" t="n">
         <v>4337520</v>
@@ -9113,10 +9122,10 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="6" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C169" s="22" t="n">
         <v>8588776</v>
@@ -9153,10 +9162,10 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="6" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C170" s="22" t="n">
         <v>8013780</v>
@@ -9193,10 +9202,10 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="6" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C171" s="22" t="n">
         <v>4491553</v>
@@ -9233,10 +9242,10 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="6" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C172" s="22" t="n">
         <v>5215809</v>
@@ -9273,10 +9282,10 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="6" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C173" s="22" t="n">
         <v>6788600</v>
@@ -9313,10 +9322,10 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="B174" s="6" t="s">
         <v>470</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>467</v>
       </c>
       <c r="C174" s="22" t="n">
         <v>6680122</v>
@@ -9353,10 +9362,10 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="6" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C175" s="22" t="n">
         <v>5188101</v>
@@ -9393,10 +9402,10 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="6" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C176" s="22" t="n">
         <v>5079812</v>
@@ -9433,10 +9442,10 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="6" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C177" s="22" t="n">
         <v>11742413</v>
@@ -9473,10 +9482,10 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="6" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C178" s="22" t="n">
         <v>4251027</v>
@@ -9513,10 +9522,10 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="6" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C179" s="22" t="n">
         <v>4413587</v>
@@ -9553,10 +9562,10 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="6" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C180" s="22" t="n">
         <v>4637351</v>
@@ -9593,10 +9602,10 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="6" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C181" s="22" t="n">
         <v>5120758</v>
@@ -9633,10 +9642,10 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="6" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C182" s="22" t="n">
         <v>7894656</v>
@@ -9673,10 +9682,10 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="6" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C183" s="22" t="n">
         <v>12048864</v>
@@ -9713,10 +9722,10 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C184" s="22" t="n">
         <v>9873978</v>
@@ -9753,10 +9762,10 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="6" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C185" s="22" t="n">
         <v>4898137</v>
@@ -9793,10 +9802,10 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="6" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C186" s="22" t="n">
         <v>21571416</v>
@@ -9833,10 +9842,10 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="6" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C187" s="22" t="n">
         <v>12392811</v>
@@ -9873,10 +9882,10 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="6" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C188" s="22" t="n">
         <v>15348450</v>
@@ -9913,10 +9922,10 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="B189" s="6" t="s">
         <v>485</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>482</v>
       </c>
       <c r="C189" s="22" t="n">
         <v>17676978</v>
@@ -9953,10 +9962,10 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="6" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C190" s="22" t="n">
         <v>13159278</v>
@@ -9993,10 +10002,10 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="6" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C191" s="22" t="n">
         <v>4450364</v>
@@ -10033,10 +10042,10 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="6" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C192" s="22" t="n">
         <v>19435568</v>
@@ -10073,10 +10082,10 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="6" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C193" s="22" t="n">
         <v>7175505</v>
@@ -10113,10 +10122,10 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="6" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C194" s="22" t="n">
         <v>11197606</v>
@@ -10153,10 +10162,10 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C195" s="22" t="n">
         <v>19247619</v>
@@ -10193,10 +10202,10 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C196" s="22" t="n">
         <v>21482425</v>
@@ -10233,10 +10242,10 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C197" s="22" t="n">
         <v>3547850</v>
@@ -10273,10 +10282,10 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="6" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C198" s="22" t="n">
         <v>5251838</v>
@@ -10313,10 +10322,10 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="6" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C199" s="22" t="n">
         <v>17890550</v>
@@ -10353,10 +10362,10 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="6" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C200" s="22" t="n">
         <v>7111460</v>
@@ -10393,10 +10402,10 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="6" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C201" s="22" t="n">
         <v>8401187</v>
@@ -10433,10 +10442,10 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C202" s="22" t="n">
         <v>5476674</v>
@@ -10473,10 +10482,10 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="6" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C203" s="22" t="n">
         <v>14959733</v>
@@ -10513,10 +10522,10 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="6" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C204" s="22" t="n">
         <v>15102719</v>
@@ -10553,10 +10562,10 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C205" s="22" t="n">
         <v>5748164</v>
@@ -10593,10 +10602,10 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="6" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C206" s="22" t="n">
         <v>7524120</v>
@@ -10633,10 +10642,10 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="B207" s="6" t="s">
         <v>503</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>500</v>
       </c>
       <c r="C207" s="22" t="n">
         <v>3992036</v>
@@ -10673,10 +10682,10 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C208" s="22" t="n">
         <v>3962483</v>
@@ -10713,10 +10722,10 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="6" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C209" s="22" t="n">
         <v>6145192</v>
@@ -10753,10 +10762,10 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="6" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C210" s="22" t="n">
         <v>8466988</v>
@@ -10793,10 +10802,10 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="6" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C211" s="22" t="n">
         <v>3177320</v>
@@ -10833,10 +10842,10 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="6" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C212" s="22" t="n">
         <v>15797015</v>
@@ -10873,10 +10882,10 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="6" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C213" s="22" t="n">
         <v>3134039</v>
@@ -10913,10 +10922,10 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="6" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C214" s="22" t="n">
         <v>4703772</v>
@@ -10953,10 +10962,10 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="6" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C215" s="22" t="n">
         <v>3551076</v>
@@ -10993,10 +11002,10 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="6" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C216" s="22" t="n">
         <v>6556473</v>
@@ -11033,10 +11042,10 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="6" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C217" s="22" t="n">
         <v>8913582</v>
@@ -11073,10 +11082,10 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="6" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C218" s="22" t="n">
         <v>7182622</v>
@@ -11113,10 +11122,10 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="6" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C219" s="22" t="n">
         <v>7461721</v>
@@ -11153,10 +11162,10 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C220" s="22" t="n">
         <v>15380854</v>
@@ -11193,10 +11202,10 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="6" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C221" s="22" t="n">
         <v>3519562</v>
@@ -11233,10 +11242,10 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="6" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C222" s="22" t="n">
         <v>12858111</v>
@@ -11273,10 +11282,10 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="6" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C223" s="22" t="n">
         <v>11357615</v>
@@ -11313,10 +11322,10 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="6" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C224" s="22" t="n">
         <v>3783423</v>
@@ -11353,10 +11362,10 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="6" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C225" s="22" t="n">
         <v>11912378</v>
@@ -11393,10 +11402,10 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="6" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C226" s="22" t="n">
         <v>1335037</v>
@@ -11433,10 +11442,10 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="6" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C227" s="22" t="n">
         <v>3662091</v>
@@ -11473,10 +11482,10 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B228" s="6" t="s">
         <v>524</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>521</v>
       </c>
       <c r="C228" s="22" t="n">
         <v>7895742</v>
@@ -11513,10 +11522,10 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C229" s="22" t="n">
         <v>5519788</v>
@@ -11553,10 +11562,10 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="6" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C230" s="22" t="n">
         <v>11986630</v>
@@ -11593,10 +11602,10 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="6" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C231" s="22" t="n">
         <v>3378496</v>
@@ -11633,10 +11642,10 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="6" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C232" s="22" t="n">
         <v>4371509</v>
@@ -11673,10 +11682,10 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="6" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C233" s="22" t="n">
         <v>12361510</v>
@@ -11713,10 +11722,10 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="6" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C234" s="22" t="n">
         <v>4602222</v>
@@ -11753,10 +11762,10 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="6" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C235" s="22" t="n">
         <v>1763393</v>
@@ -11793,10 +11802,10 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C236" s="22" t="n">
         <v>4776921</v>
@@ -11833,10 +11842,10 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="6" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C237" s="22" t="n">
         <v>4341382</v>
@@ -11873,10 +11882,10 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="6" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C238" s="22" t="n">
         <v>15941203</v>
@@ -11913,10 +11922,10 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="6" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C239" s="22" t="n">
         <v>5036348</v>
@@ -11953,10 +11962,10 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="6" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C240" s="22" t="n">
         <v>6507888</v>
@@ -11993,10 +12002,10 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="B241" s="6" t="s">
         <v>537</v>
-      </c>
-      <c r="B241" s="6" t="s">
-        <v>534</v>
       </c>
       <c r="C241" s="22" t="n">
         <v>9804277</v>
@@ -12033,10 +12042,10 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="6" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C242" s="22" t="n">
         <v>7916563</v>
@@ -12073,10 +12082,10 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="6" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C243" s="22" t="n">
         <v>6649885</v>
@@ -12113,10 +12122,10 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="6" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C244" s="22" t="n">
         <v>17231734</v>
@@ -12153,10 +12162,10 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="6" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C245" s="22" t="n">
         <v>6745424</v>
@@ -12193,10 +12202,10 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C246" s="22" t="n">
         <v>9021304</v>
@@ -12233,10 +12242,10 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="6" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C247" s="22" t="n">
         <v>5869313</v>
@@ -12273,10 +12282,10 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="6" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C248" s="22" t="n">
         <v>8987762</v>
@@ -12313,10 +12322,10 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="6" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C249" s="22" t="n">
         <v>7160615</v>
@@ -12353,10 +12362,10 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="6" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C250" s="22" t="n">
         <v>17707174</v>
@@ -12393,10 +12402,10 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="B251" s="6" t="s">
         <v>547</v>
-      </c>
-      <c r="B251" s="6" t="s">
-        <v>544</v>
       </c>
       <c r="C251" s="22" t="n">
         <v>3524632</v>
@@ -12433,10 +12442,10 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="6" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C252" s="22" t="n">
         <v>6310892</v>
@@ -12473,10 +12482,10 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="6" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C253" s="22" t="n">
         <v>11239226</v>
@@ -12513,10 +12522,10 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="6" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C254" s="22" t="n">
         <v>5727429</v>
@@ -12553,10 +12562,10 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="6" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C255" s="22" t="n">
         <v>9437826</v>
@@ -12593,10 +12602,10 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="6" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C256" s="22" t="n">
         <v>6702846</v>
@@ -12633,10 +12642,10 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="6" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C257" s="22" t="n">
         <v>5694819</v>
@@ -12673,10 +12682,10 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="6" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C258" s="22" t="n">
         <v>5321682</v>
@@ -12713,10 +12722,10 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="6" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C259" s="22" t="n">
         <v>12622822</v>
@@ -12753,10 +12762,10 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="6" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C260" s="22" t="n">
         <v>10130769</v>
@@ -12793,10 +12802,10 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C261" s="22" t="n">
         <v>13897407</v>
@@ -12833,10 +12842,10 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="6" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C262" s="22" t="n">
         <v>5263855</v>
@@ -12873,10 +12882,10 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="6" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C263" s="22" t="n">
         <v>5156201</v>
@@ -12913,10 +12922,10 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="6" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C264" s="22" t="n">
         <v>10627869</v>
@@ -12953,10 +12962,10 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="B265" s="6" t="s">
         <v>561</v>
-      </c>
-      <c r="B265" s="6" t="s">
-        <v>558</v>
       </c>
       <c r="C265" s="22" t="n">
         <v>12740133</v>
@@ -12993,10 +13002,10 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="6" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C266" s="22" t="n">
         <v>12351183</v>
@@ -13033,10 +13042,10 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="6" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C267" s="22" t="n">
         <v>8962822</v>
@@ -13073,10 +13082,10 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="6" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C268" s="22" t="n">
         <v>7463975</v>
@@ -13113,10 +13122,10 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="6" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C269" s="22" t="n">
         <v>6452517</v>
@@ -13153,10 +13162,10 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="6" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C270" s="22" t="n">
         <v>6171070</v>
@@ -13193,10 +13202,10 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="6" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C271" s="22" t="n">
         <v>5291219</v>
@@ -13233,10 +13242,10 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="6" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C272" s="22" t="n">
         <v>6754439</v>
@@ -13273,10 +13282,10 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="6" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C273" s="22" t="n">
         <v>4275564</v>
@@ -13313,10 +13322,10 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="6" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C274" s="22" t="n">
         <v>9015440</v>
@@ -13353,10 +13362,10 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="6" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C275" s="22" t="n">
         <v>5415180</v>
@@ -13393,10 +13402,10 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="6" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C276" s="22" t="n">
         <v>6248942</v>
@@ -13433,10 +13442,10 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="6" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C277" s="22" t="n">
         <v>10023543</v>
@@ -13473,10 +13482,10 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="6" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C278" s="22" t="n">
         <v>7041933</v>
@@ -13513,10 +13522,10 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="6" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C279" s="22" t="n">
         <v>5779870</v>
@@ -13553,10 +13562,10 @@
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="6" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C280" s="22" t="n">
         <v>5300226</v>
@@ -13593,10 +13602,10 @@
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="6" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C281" s="22" t="n">
         <v>6173771</v>
@@ -13633,10 +13642,10 @@
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="6" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C282" s="22" t="n">
         <v>12104552</v>
@@ -13673,10 +13682,10 @@
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="6" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C283" s="22" t="n">
         <v>3999346</v>
@@ -13713,10 +13722,10 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C284" s="22" t="n">
         <v>10514001</v>
@@ -13753,10 +13762,10 @@
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="6" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C285" s="22" t="n">
         <v>6896644</v>
@@ -13793,10 +13802,10 @@
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="6" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C286" s="22" t="n">
         <v>14218180</v>
@@ -13833,10 +13842,10 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="6" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C287" s="22" t="n">
         <v>4145950</v>
@@ -13873,10 +13882,10 @@
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="6" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C288" s="22" t="n">
         <v>1594771</v>
@@ -13913,10 +13922,10 @@
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="B289" s="6" t="s">
         <v>585</v>
-      </c>
-      <c r="B289" s="6" t="s">
-        <v>582</v>
       </c>
       <c r="C289" s="22" t="n">
         <v>7173845</v>
@@ -13953,10 +13962,10 @@
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="6" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C290" s="22" t="n">
         <v>5881607</v>
@@ -13993,10 +14002,10 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="6" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C291" s="22" t="n">
         <v>2809961</v>
@@ -14033,10 +14042,10 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="6" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C292" s="22" t="n">
         <v>3939543</v>
@@ -14073,10 +14082,10 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="6" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C293" s="22" t="n">
         <v>4683067</v>
@@ -14113,10 +14122,10 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="6" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C294" s="22" t="n">
         <v>4454145</v>
@@ -14153,10 +14162,10 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="6" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C295" s="22" t="n">
         <v>8825450</v>
@@ -14193,10 +14202,10 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="6" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C296" s="22" t="n">
         <v>5163339</v>
@@ -14233,10 +14242,10 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="6" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C297" s="22" t="n">
         <v>13471101</v>
@@ -14273,10 +14282,10 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B298" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C298" s="22" t="n">
         <v>3648879</v>
@@ -14313,10 +14322,10 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="6" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B299" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C299" s="22" t="n">
         <v>2378858</v>
@@ -14353,10 +14362,10 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="6" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C300" s="22" t="n">
         <v>3093404</v>
@@ -14393,10 +14402,10 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="6" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C301" s="22" t="n">
         <v>4147819</v>
@@ -14433,10 +14442,10 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="6" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C302" s="22" t="n">
         <v>9533245</v>
@@ -14473,10 +14482,10 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="6" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B303" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C303" s="22" t="n">
         <v>4489020</v>
@@ -14513,10 +14522,10 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="6" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B304" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C304" s="22" t="n">
         <v>6508121</v>
@@ -14553,10 +14562,10 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="6" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B305" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C305" s="22" t="n">
         <v>7664688</v>
@@ -14593,10 +14602,10 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="6" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B306" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C306" s="22" t="n">
         <v>11277641</v>
@@ -14633,10 +14642,10 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="6" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C307" s="22" t="n">
         <v>12807927</v>
@@ -14673,10 +14682,10 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="B308" s="6" t="s">
         <v>605</v>
-      </c>
-      <c r="B308" s="6" t="s">
-        <v>602</v>
       </c>
       <c r="C308" s="22" t="n">
         <v>9083994</v>
@@ -14713,10 +14722,10 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="6" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C309" s="22" t="n">
         <v>5753346</v>
@@ -14753,10 +14762,10 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="6" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C310" s="22" t="n">
         <v>3834897</v>
@@ -14793,10 +14802,10 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="6" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B311" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C311" s="22" t="n">
         <v>1927973</v>
@@ -14833,10 +14842,10 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="6" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B312" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C312" s="22" t="n">
         <v>7213282</v>
@@ -14873,10 +14882,10 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="6" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B313" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C313" s="22" t="n">
         <v>7127118</v>
@@ -14913,10 +14922,10 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="6" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C314" s="22" t="n">
         <v>7323622</v>
@@ -14953,10 +14962,10 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="6" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C315" s="22" t="n">
         <v>5213100</v>
@@ -16501,7 +16510,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>1912.6</v>
@@ -16513,7 +16522,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>0</v>
@@ -16525,7 +16534,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>16.4</v>
@@ -16537,7 +16546,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>489.7</v>
@@ -16549,7 +16558,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>75.3</v>
@@ -16612,17 +16621,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16644,7 +16653,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>47604.9</v>
@@ -16682,7 +16691,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>15147.7</v>
@@ -16701,7 +16710,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>7021.5</v>
@@ -16720,7 +16729,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>7207.9</v>
@@ -16739,7 +16748,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>673.3</v>
@@ -16777,7 +16786,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>82.3</v>
@@ -16833,17 +16842,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16865,7 +16874,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>12783.3</v>
@@ -16884,7 +16893,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>13293</v>
@@ -16903,7 +16912,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>3930.7</v>
@@ -16922,7 +16931,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>3081.9</v>
@@ -16941,7 +16950,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>1731.3</v>
@@ -16960,7 +16969,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>1455.3</v>
@@ -16979,7 +16988,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>884.1</v>
@@ -16998,7 +17007,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B29" s="7" t="n">
         <v>1201</v>
@@ -17017,7 +17026,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B30" s="7" t="n">
         <v>9244.1</v>
@@ -17073,12 +17082,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17100,7 +17109,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C38" s="7" t="n">
         <v>8184.3</v>
@@ -17112,7 +17121,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>6624.2</v>
@@ -17124,7 +17133,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C40" s="7" t="n">
         <v>2420.7</v>
@@ -17136,7 +17145,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>2160.8</v>
@@ -17148,7 +17157,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>1537.2</v>
@@ -17160,7 +17169,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C43" s="7" t="n">
         <v>1355.6</v>
@@ -17172,7 +17181,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C44" s="7" t="n">
         <v>765.2</v>
@@ -17184,7 +17193,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C45" s="7" t="n">
         <v>632.4</v>
@@ -17196,7 +17205,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>507.6</v>
@@ -17208,7 +17217,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C47" s="7" t="n">
         <v>424.4</v>
@@ -17220,7 +17229,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C48" s="7" t="n">
         <v>312</v>
@@ -17232,7 +17241,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C49" s="7" t="n">
         <v>244.4</v>
@@ -17244,7 +17253,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C50" s="7" t="n">
         <v>230.4</v>
@@ -17256,7 +17265,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C51" s="7" t="n">
         <v>172.2</v>
@@ -17268,7 +17277,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C52" s="7" t="n">
         <v>164.7</v>
@@ -17280,7 +17289,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C53" s="7" t="n">
         <v>137.5</v>
@@ -17292,7 +17301,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C54" s="7" t="n">
         <v>128.7</v>
@@ -17304,7 +17313,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C55" s="7" t="n">
         <v>26.9</v>
@@ -17316,7 +17325,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C56" s="7" t="n">
         <v>26.7</v>
@@ -17354,12 +17363,12 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17381,7 +17390,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B64" s="7" t="n">
         <v>6873.9</v>
@@ -17400,7 +17409,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B65" s="7" t="n">
         <v>72.6</v>
@@ -17419,7 +17428,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B66" s="7" t="n">
         <v>75</v>
@@ -17475,28 +17484,28 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B74" s="9" t="n">
         <v>0.558</v>
@@ -17508,7 +17517,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B75" s="9" t="n">
         <v>0.102</v>
@@ -17520,7 +17529,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B76" s="9" t="n">
         <v>0.068</v>
@@ -17532,7 +17541,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B77" s="8" t="n">
         <f aca="false">1-SUM(B74:B76)</f>
@@ -17545,7 +17554,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C78" s="7" t="n">
         <v>15110.1</v>
@@ -17553,28 +17562,28 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B83" s="9" t="n">
         <v>0.544</v>
@@ -17586,7 +17595,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B84" s="9" t="n">
         <v>0.131</v>
@@ -17598,7 +17607,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B85" s="9" t="n">
         <v>0.103</v>
@@ -17610,7 +17619,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B86" s="8" t="n">
         <f aca="false">1-SUM(B83:B85)</f>
@@ -17623,7 +17632,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C87" s="7" t="n">
         <v>6557.9</v>
@@ -17631,28 +17640,28 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B92" s="9" t="n">
         <v>0.602</v>
@@ -17664,7 +17673,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B93" s="8" t="n">
         <f aca="false">1-SUM(B92)</f>
@@ -17677,7 +17686,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C94" s="7" t="n">
         <v>991.9</v>
@@ -17713,49 +17722,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>28046.6</v>
@@ -17781,7 +17790,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>324</v>
@@ -17789,7 +17798,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>18062.4</v>
@@ -17815,7 +17824,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J6" s="18" t="n">
         <v>303</v>
@@ -17823,7 +17832,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>10707</v>
@@ -17849,7 +17858,7 @@
         <v>464.5</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>196</v>
@@ -17857,7 +17866,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>7088.1</v>
@@ -17876,7 +17885,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J8" s="18" t="n">
         <v>200</v>
@@ -17884,7 +17893,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>7670.9</v>
@@ -17910,7 +17919,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>289</v>
@@ -17918,7 +17927,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>7451.3</v>
@@ -17944,7 +17953,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J10" s="18" t="n">
         <v>157</v>
@@ -17952,7 +17961,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>6068.5</v>
@@ -17978,7 +17987,7 @@
         <v>49.8</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>250</v>
@@ -17986,7 +17995,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>3860.9</v>
@@ -18012,7 +18021,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J12" s="18" t="n">
         <v>236</v>
@@ -18020,7 +18029,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>4118.3</v>
@@ -18046,7 +18055,7 @@
         <v>32.7</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>292</v>
@@ -18054,7 +18063,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>2884.6</v>
@@ -18080,7 +18089,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J14" s="18" t="n">
         <v>275</v>
@@ -18088,7 +18097,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>2290.4</v>
@@ -18114,7 +18123,7 @@
         <v>513.7</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>333</v>
@@ -18122,7 +18131,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>1947.3</v>
@@ -18148,7 +18157,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J16" s="18" t="n">
         <v>264</v>
@@ -18156,7 +18165,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B17" s="7" t="n">
         <v>1813</v>
@@ -18182,7 +18191,7 @@
         <v>22.3</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>357</v>
@@ -18190,7 +18199,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B18" s="7" t="n">
         <v>2312.1</v>
@@ -18216,7 +18225,7 @@
         <v>532.4</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J18" s="18" t="n">
         <v>212</v>
@@ -18224,7 +18233,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B19" s="7" t="n">
         <v>672</v>
@@ -18250,7 +18259,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>169</v>
@@ -18258,7 +18267,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B20" s="7" t="n">
         <v>607</v>
@@ -18284,7 +18293,7 @@
         <v>13</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J20" s="18" t="n">
         <v>346</v>
@@ -18292,7 +18301,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>487.5</v>
@@ -18318,7 +18327,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>180</v>
@@ -18326,7 +18335,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>1194.5</v>
@@ -18352,7 +18361,7 @@
         <v>38.7</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J22" s="18" t="n">
         <v>214</v>
@@ -18360,7 +18369,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>156.2</v>
@@ -18386,7 +18395,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J23" s="18" t="n">
         <v>348</v>
@@ -18394,7 +18403,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>250.3</v>
@@ -18420,7 +18429,7 @@
         <v>10.8</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J24" s="18" t="n">
         <v>224</v>
@@ -18484,7 +18493,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -18515,34 +18524,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>322538.2</v>
@@ -18550,7 +18559,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>64738.2</v>
@@ -18558,7 +18567,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>257800</v>
@@ -18574,7 +18583,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>1833.9</v>
@@ -18582,7 +18591,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>259633.9</v>
@@ -18598,7 +18607,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>153554.4</v>
@@ -18606,7 +18615,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>2.4</v>
@@ -18614,7 +18623,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>106081.9</v>
@@ -18630,7 +18639,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>8380.4</v>
@@ -18638,7 +18647,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>97701.5</v>
@@ -18654,26 +18663,26 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">B12/'Visão geral'!C11</f>
         <v>0.311511750489665</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">B14/'Visão geral'!C11</f>
         <v>0.286902528051119</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -18692,7 +18701,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -18704,7 +18713,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18714,7 +18723,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18722,21 +18731,21 @@
         <v>83</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>32361.1</v>
@@ -18755,7 +18764,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>10411.1</v>
@@ -18774,7 +18783,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>1763.3</v>
@@ -18793,7 +18802,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>1192.8</v>
@@ -18812,7 +18821,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>1046</v>
@@ -18831,7 +18840,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>493.6</v>
@@ -18863,7 +18872,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>49795.2</v>
@@ -18874,7 +18883,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B14" s="13" t="n">
         <f aca="false">B13-B12</f>
@@ -18887,17 +18896,17 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18905,10 +18914,10 @@
         <v>83</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>27</v>
@@ -18917,7 +18926,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B20" s="7" t="n">
         <v>25436</v>
@@ -18932,7 +18941,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>3991.7</v>
@@ -18947,7 +18956,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>1587.3</v>
@@ -18962,7 +18971,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>1102.9</v>
@@ -18977,7 +18986,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>1376.3</v>
@@ -18992,7 +19001,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>1088</v>
@@ -19007,7 +19016,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>930.5</v>
@@ -19022,7 +19031,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>667.1</v>
@@ -19037,7 +19046,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>613.7</v>
@@ -19052,7 +19061,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B29" s="7" t="n">
         <v>476.5</v>
@@ -19080,7 +19089,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B31" s="7" t="n">
         <v>42032.3</v>
@@ -19091,7 +19100,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B32" s="13" t="n">
         <f aca="false">B31-B30</f>
@@ -19104,7 +19113,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B34" s="7" t="n">
         <v>7762.9</v>
@@ -19124,6 +19133,11 @@
       <c r="C35" s="15" t="n">
         <f aca="false">C13-C31</f>
         <v>8382.7</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -19154,29 +19168,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19187,7 +19201,7 @@
         <v>114</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>300</v>
@@ -19205,7 +19219,7 @@
         <v>114</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>-94</v>
@@ -19223,7 +19237,7 @@
         <v>115</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>-431</v>
@@ -19241,7 +19255,7 @@
         <v>115</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>284</v>
@@ -19259,7 +19273,7 @@
         <v>115</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>-209</v>
@@ -19277,7 +19291,7 @@
         <v>115</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>-121</v>
@@ -19295,7 +19309,7 @@
         <v>116</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>-300</v>
@@ -19313,7 +19327,7 @@
         <v>116</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>124</v>
@@ -19328,10 +19342,10 @@
         <v>81</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>363</v>
@@ -19346,10 +19360,10 @@
         <v>91</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>587</v>
@@ -19364,10 +19378,10 @@
         <v>91</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>244</v>
@@ -19382,10 +19396,10 @@
         <v>91</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>116</v>
@@ -19400,10 +19414,10 @@
         <v>91</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>100</v>
@@ -19415,7 +19429,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="11" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D19" s="12" t="n">
         <f aca="false">SUMIF(A5:A17,"Receita",D5:D17)</f>
@@ -19424,7 +19438,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="11" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D20" s="12" t="n">
         <f aca="false">SUMIF(A5:A17,"Despesa",D5:D17)</f>
@@ -19433,7 +19447,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E21" s="12" t="n">
         <f aca="false">SUM(E5:E17)</f>
@@ -19442,7 +19456,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>-84</v>
@@ -19450,7 +19464,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>1048</v>
@@ -19458,7 +19472,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>-1132</v>
@@ -19466,7 +19480,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D25" s="13" t="n">
         <f aca="false">D19-D22</f>
@@ -19479,7 +19493,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D26" s="13" t="n">
         <f aca="false">D20-D23</f>
@@ -19488,7 +19502,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="10" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
